--- a/data/trans_orig/KC10IN_T-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Estudios-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN autopercibido (escala)</t>
+          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,82; 62,1</t>
+          <t>53,14; 62,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,94; 58,02</t>
+          <t>48,41; 58,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,47; 57,95</t>
+          <t>51,3; 57,55</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,29; 58,4</t>
+          <t>54,43; 58,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,86; 63,65</t>
+          <t>56,81; 63,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,42; 60,49</t>
+          <t>56,32; 60,77</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,81; 62,94</t>
+          <t>57,92; 62,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,66; 64,73</t>
+          <t>58,8; 65,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,8; 63,09</t>
+          <t>58,99; 63,1</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,24; 58,75</t>
+          <t>55,03; 58,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57,44; 63,15</t>
+          <t>57,44; 62,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,9; 60,29</t>
+          <t>57,0; 60,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Estudios-trans_orig.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,14; 62,84</t>
+          <t>52,75; 61,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,41; 58,02</t>
+          <t>48,72; 57,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,3; 57,55</t>
+          <t>51,15; 57,53</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,43; 58,39</t>
+          <t>54,31; 58,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,81; 63,22</t>
+          <t>56,79; 63,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,32; 60,77</t>
+          <t>56,34; 60,64</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,92; 62,89</t>
+          <t>57,88; 62,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,8; 65,18</t>
+          <t>58,69; 65,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,99; 63,1</t>
+          <t>59,0; 63,17</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,03; 58,74</t>
+          <t>55,01; 58,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57,44; 62,69</t>
+          <t>57,3; 62,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57,0; 60,47</t>
+          <t>57,09; 60,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Estudios-trans_orig.xlsx
@@ -495,12 +495,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>56,35</t>
+          <t>52,36</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>52,15</t>
+          <t>55,98</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54,03</t>
+          <t>54,09</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,75; 61,61</t>
+          <t>49,04; 58,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,72; 57,98</t>
+          <t>52,49; 61,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,15; 57,53</t>
+          <t>51,58; 57,85</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>56,65</t>
+          <t>58,8</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59,2</t>
+          <t>57,5</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58,08</t>
+          <t>58,27</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,31; 58,41</t>
+          <t>56,69; 62,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,79; 63,4</t>
+          <t>56,03; 59,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,34; 60,64</t>
+          <t>56,92; 60,48</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>60,15</t>
+          <t>61,32</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>61,49</t>
+          <t>60,09</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60,91</t>
+          <t>60,78</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,88; 62,59</t>
+          <t>58,51; 64,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,69; 65,08</t>
+          <t>57,75; 62,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,0; 63,17</t>
+          <t>58,69; 62,96</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>57,28</t>
+          <t>58,93</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>59,24</t>
+          <t>57,94</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58,38</t>
+          <t>58,51</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,01; 58,64</t>
+          <t>57,29; 62,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57,3; 62,15</t>
+          <t>56,75; 59,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57,09; 60,49</t>
+          <t>57,36; 60,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 29,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -546,149 +551,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>52,36</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>55,98</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>54,09</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>52.35525316085668</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>55.98471854493145</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>54.08793473466891</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>49,04; 58,22</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>52,49; 61,56</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>51,58; 57,85</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>49.04332274048358</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>52.49105113597014</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>51.58483687462218</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>58.21584981377573</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>61.55621818441223</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>57.84622189106428</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>58,8</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57,5</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>58,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>56,69; 62,48</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>56,03; 59,08</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>56,92; 60,48</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>58.80472120996608</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>57.50174563030025</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>58.26540319938825</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>61,32</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>60,09</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>60,78</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>56.69240444938301</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>56.03496457747644</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>56.9199784024643</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>58,51; 64,67</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>57,75; 62,95</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>58,69; 62,96</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>62.4820067893659</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>59.08036441219662</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>60.48128853587539</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -696,47 +661,107 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>58,93</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>57,94</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>58,51</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>61.31937067462334</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>60.09310342886069</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>60.7790689031004</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>57,29; 62,02</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>56,75; 59,14</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57,36; 60,14</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>58.50869267180947</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>57.7465072076679</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>58.6884968063959</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>64.67443377638266</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>62.94879654062244</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>62.95797784654133</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>58.92573356494936</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>57.93558560135788</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>58.50662137489838</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>57.28806576354001</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>56.74706226701043</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>57.3591037734431</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>62.02226257352562</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>59.1375121271623</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>60.13804743013878</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -744,11 +769,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
